--- a/outputs/evaluation/requirement/design/v1/CF_M01/first/CF_M01_req_eval_by_type.xlsx
+++ b/outputs/evaluation/requirement/design/v1/CF_M01/first/CF_M01_req_eval_by_type.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,11 +457,6 @@
           <t>recall</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -490,9 +485,6 @@
       <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -521,9 +513,6 @@
       <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,9 +541,6 @@
       <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -582,9 +568,6 @@
       </c>
       <c r="H5" t="n">
         <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.6667</v>
       </c>
     </row>
   </sheetData>
